--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>Exdata.xlsx</t>
+  </si>
+  <si>
+    <t>demo.IconRecord</t>
+  </si>
+  <si>
+    <t>demo.Icon</t>
+  </si>
+  <si>
+    <t>Icon.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1067,8 +1076,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1195,6 +1204,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6" spans="2:5">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>Icon.xlsx</t>
+  </si>
+  <si>
+    <t>demo.HomeTabRecord</t>
+  </si>
+  <si>
+    <t>demp.HomeTab</t>
+  </si>
+  <si>
+    <t>HomeTab.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1085,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1218,6 +1227,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="2:5">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="8700"/>
+    <workbookView windowWidth="26880" windowHeight="9285"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
     <t>demo.HomeTabRecord</t>
   </si>
   <si>
-    <t>demp.HomeTab</t>
+    <t>demo.HomeTab</t>
   </si>
   <si>
     <t>HomeTab.xlsx</t>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>HomeTab.xlsx</t>
+  </si>
+  <si>
+    <t>demo.DictionaryRecord</t>
+  </si>
+  <si>
+    <t>demo.Dictionary</t>
+  </si>
+  <si>
+    <t>Dictionary.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1085,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1241,6 +1250,20 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="2:5">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,9 @@
     <t>full_name</t>
   </si>
   <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>value_type</t>
   </si>
   <si>
@@ -62,12 +65,12 @@
     <t>output</t>
   </si>
   <si>
-    <t>##</t>
-  </si>
-  <si>
     <t>全名(包含模块和名字)</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>记录类名</t>
   </si>
   <si>
@@ -110,49 +113,79 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>demo.GlobalSettingRecord</t>
-  </si>
-  <si>
-    <t>demo.GlobalSetting</t>
+    <t>通用配置</t>
+  </si>
+  <si>
+    <t>Common.GlobalSettingRecord</t>
+  </si>
+  <si>
+    <t>全局表</t>
+  </si>
+  <si>
+    <t>GlobalSetting</t>
   </si>
   <si>
     <t>GlobalSetting.xlsx</t>
   </si>
   <si>
-    <t>demo.ExdataRecord</t>
-  </si>
-  <si>
-    <t>demo.Exdata</t>
+    <t>Common.ExdataRecord</t>
+  </si>
+  <si>
+    <t>Exdata</t>
   </si>
   <si>
     <t>Exdata.xlsx</t>
   </si>
   <si>
-    <t>demo.IconRecord</t>
-  </si>
-  <si>
-    <t>demo.Icon</t>
+    <t>Common.TextRecord</t>
+  </si>
+  <si>
+    <t>文字表</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Text.xlsx</t>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
+    <t>Res.ItemRecord</t>
+  </si>
+  <si>
+    <t>物品表</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Item.xlsx</t>
+  </si>
+  <si>
+    <t>Res.IconRecord</t>
+  </si>
+  <si>
+    <t>图标表</t>
+  </si>
+  <si>
+    <t>Icon</t>
   </si>
   <si>
     <t>Icon.xlsx</t>
   </si>
   <si>
-    <t>demo.HomeTabRecord</t>
-  </si>
-  <si>
-    <t>demo.HomeTab</t>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>UI.HomeTabRecord</t>
+  </si>
+  <si>
+    <t>HomeTab</t>
   </si>
   <si>
     <t>HomeTab.xlsx</t>
-  </si>
-  <si>
-    <t>demo.DictionaryRecord</t>
-  </si>
-  <si>
-    <t>demo.Dictionary</t>
-  </si>
-  <si>
-    <t>Dictionary.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1094,17 +1127,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="5" max="5" width="32.375" customWidth="1"/>
+    <col min="6" max="6" width="24.375" customWidth="1"/>
+    <col min="7" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,10 +1172,13 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -1167,16 +1204,16 @@
       <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>22</v>
@@ -1190,78 +1227,134 @@
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="b">
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="F5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:6">
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:6">
       <c r="B7" t="s">
         <v>36</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>38</v>
+      <c r="F7" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="b">
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="2:6">
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="2:6">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowWidth="30705" windowHeight="9885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -116,61 +116,82 @@
     <t>通用配置</t>
   </si>
   <si>
-    <t>Common.GlobalSettingRecord</t>
+    <t>Common.GlobalSetting</t>
   </si>
   <si>
     <t>全局表</t>
   </si>
   <si>
-    <t>GlobalSetting</t>
+    <t>GlobalSettingRecord</t>
   </si>
   <si>
     <t>GlobalSetting.xlsx</t>
   </si>
   <si>
-    <t>Common.ExdataRecord</t>
+    <t>Common.Flag</t>
+  </si>
+  <si>
+    <t>FlagRecord</t>
+  </si>
+  <si>
+    <t>Flag.xlsx</t>
+  </si>
+  <si>
+    <t>Common.ExtendData</t>
   </si>
   <si>
     <t>Exdata</t>
   </si>
   <si>
+    <t>ExDataRecord</t>
+  </si>
+  <si>
     <t>Exdata.xlsx</t>
   </si>
   <si>
-    <t>Common.TextRecord</t>
+    <t>Common.Condition</t>
+  </si>
+  <si>
+    <t>ConditionRecord</t>
+  </si>
+  <si>
+    <t>Condition.xlsx</t>
+  </si>
+  <si>
+    <t>Common.Dictionary</t>
   </si>
   <si>
     <t>文字表</t>
   </si>
   <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>Text.xlsx</t>
+    <t>DictionaryRecord</t>
+  </si>
+  <si>
+    <t>Dictionary.xlsx</t>
   </si>
   <si>
     <t>资源</t>
   </si>
   <si>
-    <t>Res.ItemRecord</t>
+    <t>Res.Item</t>
   </si>
   <si>
     <t>物品表</t>
   </si>
   <si>
-    <t>Item</t>
+    <t>ItemRecord</t>
   </si>
   <si>
     <t>Item.xlsx</t>
   </si>
   <si>
-    <t>Res.IconRecord</t>
+    <t>Res.Icon</t>
   </si>
   <si>
     <t>图标表</t>
   </si>
   <si>
-    <t>Icon</t>
+    <t>IconRecord</t>
   </si>
   <si>
     <t>Icon.xlsx</t>
@@ -179,10 +200,10 @@
     <t>UI</t>
   </si>
   <si>
-    <t>UI.HomeTabRecord</t>
-  </si>
-  <si>
-    <t>HomeTab</t>
+    <t>UI.HomeTab</t>
+  </si>
+  <si>
+    <t>HomeTabRecord</t>
   </si>
   <si>
     <t>HomeTab.xlsx</t>
@@ -1127,12 +1148,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.625" customWidth="1"/>
     <col min="3" max="3" width="20.375" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="4" max="4" width="29.5" customWidth="1"/>
     <col min="5" max="5" width="32.375" customWidth="1"/>
     <col min="6" max="6" width="24.375" customWidth="1"/>
     <col min="7" max="10" width="18" customWidth="1"/>
@@ -1263,9 +1284,6 @@
       <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
       <c r="D6" t="s">
         <v>34</v>
       </c>
@@ -1293,68 +1311,99 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="2:6">
+      <c r="B8" t="s">
         <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="2:6">
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
+    <row r="10" s="1" customFormat="1" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E10" t="b">
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
+      <c r="F11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="2:6">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="2:6">
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30705" windowHeight="9885"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -207,6 +207,27 @@
   </si>
   <si>
     <t>HomeTab.xlsx</t>
+  </si>
+  <si>
+    <t>合成</t>
+  </si>
+  <si>
+    <t>Merge.MergeItem</t>
+  </si>
+  <si>
+    <t>MergeItemRecord</t>
+  </si>
+  <si>
+    <t>MergeItem.xlsx</t>
+  </si>
+  <si>
+    <t>Merge.MergeFormula</t>
+  </si>
+  <si>
+    <t>MergeFormulaRecord</t>
+  </si>
+  <si>
+    <t>MergeFormula.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.625" customWidth="1"/>
@@ -1406,6 +1427,42 @@
         <v>59</v>
       </c>
     </row>
+    <row r="15" s="1" customFormat="1" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -228,6 +228,18 @@
   </si>
   <si>
     <t>MergeFormula.xlsx</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>Shop.Store</t>
+  </si>
+  <si>
+    <t>StoreRecord</t>
+  </si>
+  <si>
+    <t>Store.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.625" customWidth="1"/>
@@ -1463,6 +1475,28 @@
         <v>66</v>
       </c>
     </row>
+    <row r="18" s="1" customFormat="1" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
